--- a/research/traditional_assets/database/data/peru/peru_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_insurance_general.xlsx
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0682</v>
+        <v>0.0711</v>
       </c>
       <c r="E2">
-        <v>-0.144</v>
+        <v>0.0692</v>
       </c>
       <c r="G2">
-        <v>0.06641101621056301</v>
+        <v>0.02146911244550465</v>
       </c>
       <c r="H2">
-        <v>0.06641101621056301</v>
+        <v>0.02146911244550465</v>
       </c>
       <c r="I2">
-        <v>0.01952239846609726</v>
+        <v>0.04844945299004688</v>
       </c>
       <c r="J2">
-        <v>0.01585272425271059</v>
+        <v>0.04361153954198414</v>
       </c>
       <c r="K2">
-        <v>23.6</v>
+        <v>61.9</v>
       </c>
       <c r="L2">
-        <v>0.02056824124106676</v>
+        <v>0.05091716706424282</v>
       </c>
       <c r="M2">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.03350837709427357</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.5677966101694915</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.03350837709427357</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.5677966101694915</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>317.7</v>
+        <v>169.1</v>
       </c>
       <c r="V2">
-        <v>0.7944486121530383</v>
+        <v>0.4775487150522451</v>
       </c>
       <c r="W2">
-        <v>0.03856209150326798</v>
+        <v>0.1233067729083665</v>
       </c>
       <c r="X2">
-        <v>0.05872750427978357</v>
+        <v>0.09529087975596018</v>
       </c>
       <c r="Y2">
-        <v>-0.0201654127765156</v>
+        <v>0.02801589315240635</v>
       </c>
       <c r="Z2">
-        <v>2.745501531393568</v>
+        <v>5.198187026980801</v>
       </c>
       <c r="AA2">
-        <v>0.04352367871257689</v>
+        <v>0.2267009390738022</v>
       </c>
       <c r="AB2">
-        <v>0.05566271404071396</v>
+        <v>0.09194312919902414</v>
       </c>
       <c r="AC2">
-        <v>-0.01213903532813707</v>
+        <v>0.1347578098747781</v>
       </c>
       <c r="AD2">
-        <v>50.6</v>
+        <v>32.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>50.6</v>
+        <v>32.3</v>
       </c>
       <c r="AG2">
-        <v>-267.1</v>
+        <v>-136.8</v>
       </c>
       <c r="AH2">
-        <v>0.1123196448390677</v>
+        <v>0.08359213250517597</v>
       </c>
       <c r="AI2">
-        <v>0.09146782357194504</v>
+        <v>0.05814581458145814</v>
       </c>
       <c r="AJ2">
-        <v>-2.011295180722891</v>
+        <v>-0.6295444086516337</v>
       </c>
       <c r="AK2">
-        <v>-1.134182590233545</v>
+        <v>-0.3540372670807453</v>
       </c>
       <c r="AL2">
-        <v>2.19</v>
+        <v>5.58</v>
       </c>
       <c r="AM2">
-        <v>2.19</v>
+        <v>5.58</v>
       </c>
       <c r="AN2">
-        <v>1.611464968152866</v>
+        <v>0.4167741935483871</v>
       </c>
       <c r="AO2">
-        <v>10.2283105022831</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="AP2">
-        <v>-8.506369426751592</v>
+        <v>-1.765161290322581</v>
       </c>
       <c r="AQ2">
-        <v>10.2283105022831</v>
+        <v>10.55555555555556</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0682</v>
+        <v>0.0711</v>
       </c>
       <c r="E3">
-        <v>-0.144</v>
+        <v>0.0692</v>
       </c>
       <c r="G3">
-        <v>0.06641101621056301</v>
+        <v>0.02146911244550465</v>
       </c>
       <c r="H3">
-        <v>0.06641101621056301</v>
+        <v>0.02146911244550465</v>
       </c>
       <c r="I3">
-        <v>0.01952239846609726</v>
+        <v>0.04844945299004688</v>
       </c>
       <c r="J3">
-        <v>0.01585272425271059</v>
+        <v>0.04361153954198414</v>
       </c>
       <c r="K3">
-        <v>23.6</v>
+        <v>61.9</v>
       </c>
       <c r="L3">
-        <v>0.02056824124106676</v>
+        <v>0.05091716706424282</v>
       </c>
       <c r="M3">
-        <v>13.4</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03350837709427357</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.5677966101694915</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>13.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03350837709427357</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.5677966101694915</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>317.7</v>
+        <v>169.1</v>
       </c>
       <c r="V3">
-        <v>0.7944486121530383</v>
+        <v>0.4775487150522451</v>
       </c>
       <c r="W3">
-        <v>0.03856209150326798</v>
+        <v>0.1233067729083665</v>
       </c>
       <c r="X3">
-        <v>0.05872750427978357</v>
+        <v>0.09529087975596018</v>
       </c>
       <c r="Y3">
-        <v>-0.0201654127765156</v>
+        <v>0.02801589315240635</v>
       </c>
       <c r="Z3">
-        <v>2.745501531393568</v>
+        <v>5.198187026980801</v>
       </c>
       <c r="AA3">
-        <v>0.04352367871257689</v>
+        <v>0.2267009390738022</v>
       </c>
       <c r="AB3">
-        <v>0.05566271404071396</v>
+        <v>0.09194312919902414</v>
       </c>
       <c r="AC3">
-        <v>-0.01213903532813707</v>
+        <v>0.1347578098747781</v>
       </c>
       <c r="AD3">
-        <v>50.6</v>
+        <v>32.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>50.6</v>
+        <v>32.3</v>
       </c>
       <c r="AG3">
-        <v>-267.1</v>
+        <v>-136.8</v>
       </c>
       <c r="AH3">
-        <v>0.1123196448390677</v>
+        <v>0.08359213250517597</v>
       </c>
       <c r="AI3">
-        <v>0.09146782357194504</v>
+        <v>0.05814581458145814</v>
       </c>
       <c r="AJ3">
-        <v>-2.011295180722891</v>
+        <v>-0.6295444086516337</v>
       </c>
       <c r="AK3">
-        <v>-1.134182590233545</v>
+        <v>-0.3540372670807453</v>
       </c>
       <c r="AL3">
-        <v>2.19</v>
+        <v>5.58</v>
       </c>
       <c r="AM3">
-        <v>2.19</v>
+        <v>5.58</v>
       </c>
       <c r="AN3">
-        <v>1.611464968152866</v>
+        <v>0.4167741935483871</v>
       </c>
       <c r="AO3">
-        <v>10.2283105022831</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="AP3">
-        <v>-8.506369426751592</v>
+        <v>-1.765161290322581</v>
       </c>
       <c r="AQ3">
-        <v>10.2283105022831</v>
+        <v>10.55555555555556</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/peru/peru_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0711</v>
+        <v>0.0722</v>
       </c>
       <c r="E2">
-        <v>0.0692</v>
+        <v>0.3415</v>
       </c>
       <c r="G2">
-        <v>0.02146911244550465</v>
+        <v>0.07691525078848306</v>
       </c>
       <c r="H2">
-        <v>0.02146911244550465</v>
+        <v>0.07691525078848306</v>
       </c>
       <c r="I2">
-        <v>0.04844945299004688</v>
+        <v>0.095279275612982</v>
       </c>
       <c r="J2">
-        <v>0.04361153954198414</v>
+        <v>0.09327139380658597</v>
       </c>
       <c r="K2">
-        <v>61.9</v>
+        <v>134.7</v>
       </c>
       <c r="L2">
-        <v>0.05091716706424282</v>
+        <v>0.06852172143656528</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>22.01</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04113249859839282</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.1634001484780995</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>22.01</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.04113249859839282</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.1634001484780995</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>169.1</v>
+        <v>252.4</v>
       </c>
       <c r="V2">
-        <v>0.4775487150522451</v>
+        <v>0.4716875350401794</v>
       </c>
       <c r="W2">
-        <v>0.1233067729083665</v>
+        <v>0.1929456902570409</v>
       </c>
       <c r="X2">
-        <v>0.09529087975596018</v>
+        <v>0.08304214788320198</v>
       </c>
       <c r="Y2">
-        <v>0.02801589315240635</v>
+        <v>0.109903542373839</v>
       </c>
       <c r="Z2">
-        <v>5.198187026980801</v>
+        <v>4.475050081952285</v>
       </c>
       <c r="AA2">
-        <v>0.2267009390738022</v>
+        <v>0.6861161529746597</v>
       </c>
       <c r="AB2">
-        <v>0.09194312919902414</v>
+        <v>0.0817475200466477</v>
       </c>
       <c r="AC2">
-        <v>0.1347578098747781</v>
+        <v>0.604368632928012</v>
       </c>
       <c r="AD2">
-        <v>32.3</v>
+        <v>29.42</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>32.3</v>
+        <v>29.42</v>
       </c>
       <c r="AG2">
-        <v>-136.8</v>
+        <v>-222.98</v>
       </c>
       <c r="AH2">
-        <v>0.08359213250517597</v>
+        <v>0.05211507121094026</v>
       </c>
       <c r="AI2">
-        <v>0.05814581458145814</v>
+        <v>0.03032614521914814</v>
       </c>
       <c r="AJ2">
-        <v>-0.6295444086516337</v>
+        <v>-0.71440471613482</v>
       </c>
       <c r="AK2">
-        <v>-0.3540372670807453</v>
+        <v>-0.3106782589310595</v>
       </c>
       <c r="AL2">
-        <v>5.58</v>
+        <v>11.74</v>
       </c>
       <c r="AM2">
-        <v>5.58</v>
+        <v>11.74</v>
       </c>
       <c r="AN2">
-        <v>0.4167741935483871</v>
+        <v>0.1386427898209237</v>
       </c>
       <c r="AO2">
-        <v>10.55555555555556</v>
+        <v>15.95400340715503</v>
       </c>
       <c r="AP2">
-        <v>-1.765161290322581</v>
+        <v>-1.050801131008483</v>
       </c>
       <c r="AQ2">
-        <v>10.55555555555556</v>
+        <v>15.95400340715503</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RIMAC Seguros y Reaseguros S.A. (BVL:RIMSEGC1)</t>
+          <t>La Positiva Seguros y Reaseguros S.A. (BVL:POSITIC1)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,118 +722,255 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0711</v>
+        <v>0.0616</v>
       </c>
       <c r="E3">
-        <v>0.0692</v>
+        <v>0.187</v>
       </c>
       <c r="G3">
-        <v>0.02146911244550465</v>
+        <v>0.05067628494138864</v>
       </c>
       <c r="H3">
-        <v>0.02146911244550465</v>
+        <v>0.05067628494138864</v>
       </c>
       <c r="I3">
-        <v>0.04844945299004688</v>
+        <v>0.1033363390441839</v>
       </c>
       <c r="J3">
-        <v>0.04361153954198414</v>
+        <v>0.1033363390441839</v>
       </c>
       <c r="K3">
-        <v>61.9</v>
+        <v>26.8</v>
       </c>
       <c r="L3">
-        <v>0.05091716706424282</v>
+        <v>0.04833183047790802</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.91</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01896722939424032</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.07126865671641791</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.91</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01896722939424032</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.07126865671641791</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>169.1</v>
+        <v>54.9</v>
       </c>
       <c r="V3">
-        <v>0.4775487150522451</v>
+        <v>0.5451837140019861</v>
       </c>
       <c r="W3">
-        <v>0.1233067729083665</v>
+        <v>0.179384203480589</v>
       </c>
       <c r="X3">
-        <v>0.09529087975596018</v>
+        <v>0.08205213305011502</v>
       </c>
       <c r="Y3">
-        <v>0.02801589315240635</v>
+        <v>0.09733207043047401</v>
       </c>
       <c r="Z3">
-        <v>5.198187026980801</v>
+        <v>10.14638609332113</v>
       </c>
       <c r="AA3">
-        <v>0.2267009390738022</v>
+        <v>1.048490393412626</v>
       </c>
       <c r="AB3">
-        <v>0.09194312919902414</v>
+        <v>0.08198228590629576</v>
       </c>
       <c r="AC3">
-        <v>0.1347578098747781</v>
+        <v>0.96650810750633</v>
       </c>
       <c r="AD3">
-        <v>32.3</v>
+        <v>0.22</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>32.3</v>
+        <v>0.22</v>
       </c>
       <c r="AG3">
-        <v>-136.8</v>
+        <v>-54.68</v>
       </c>
       <c r="AH3">
-        <v>0.08359213250517597</v>
+        <v>0.002179944510503369</v>
       </c>
       <c r="AI3">
-        <v>0.05814581458145814</v>
+        <v>0.0007724176672986446</v>
       </c>
       <c r="AJ3">
-        <v>-0.6295444086516337</v>
+        <v>-1.188179052585832</v>
       </c>
       <c r="AK3">
-        <v>-0.3540372670807453</v>
+        <v>-0.237821851078636</v>
       </c>
       <c r="AL3">
-        <v>5.58</v>
+        <v>3.16</v>
       </c>
       <c r="AM3">
-        <v>5.58</v>
+        <v>3.16</v>
       </c>
       <c r="AN3">
-        <v>0.4167741935483871</v>
+        <v>0.003660565723793677</v>
       </c>
       <c r="AO3">
-        <v>10.55555555555556</v>
+        <v>18.13291139240506</v>
       </c>
       <c r="AP3">
-        <v>-1.765161290322581</v>
+        <v>-0.9098169717138103</v>
       </c>
       <c r="AQ3">
-        <v>10.55555555555556</v>
+        <v>18.13291139240506</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RIMAC Seguros y Reaseguros S.A. (BVL:RIMSEGC1)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0828</v>
+      </c>
+      <c r="E4">
+        <v>0.496</v>
+      </c>
+      <c r="G4">
+        <v>0.08722454474597888</v>
+      </c>
+      <c r="H4">
+        <v>0.08722454474597888</v>
+      </c>
+      <c r="I4">
+        <v>0.09211365407780062</v>
+      </c>
+      <c r="J4">
+        <v>0.08823131284559518</v>
+      </c>
+      <c r="K4">
+        <v>107.9</v>
+      </c>
+      <c r="L4">
+        <v>0.07645433288457451</v>
+      </c>
+      <c r="M4">
+        <v>20.1</v>
+      </c>
+      <c r="N4">
+        <v>0.04627071823204421</v>
+      </c>
+      <c r="O4">
+        <v>0.1862835959221501</v>
+      </c>
+      <c r="P4">
+        <v>20.1</v>
+      </c>
+      <c r="Q4">
+        <v>0.04627071823204421</v>
+      </c>
+      <c r="R4">
+        <v>0.1862835959221501</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>197.5</v>
+      </c>
+      <c r="V4">
+        <v>0.4546500920810314</v>
+      </c>
+      <c r="W4">
+        <v>0.2065071770334928</v>
+      </c>
+      <c r="X4">
+        <v>0.08403216271628894</v>
+      </c>
+      <c r="Y4">
+        <v>0.1224750143172039</v>
+      </c>
+      <c r="Z4">
+        <v>3.669240568858384</v>
+      </c>
+      <c r="AA4">
+        <v>0.3237419125366937</v>
+      </c>
+      <c r="AB4">
+        <v>0.08151275418699964</v>
+      </c>
+      <c r="AC4">
+        <v>0.242229158349694</v>
+      </c>
+      <c r="AD4">
+        <v>29.2</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>29.2</v>
+      </c>
+      <c r="AG4">
+        <v>-168.3</v>
+      </c>
+      <c r="AH4">
+        <v>0.06298533218291631</v>
+      </c>
+      <c r="AI4">
+        <v>0.04260907631694148</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.632468996617813</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3450184501845018</v>
+      </c>
+      <c r="AL4">
+        <v>8.58</v>
+      </c>
+      <c r="AM4">
+        <v>8.58</v>
+      </c>
+      <c r="AN4">
+        <v>0.1919789612097304</v>
+      </c>
+      <c r="AO4">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="AP4">
+        <v>-1.106508875739645</v>
+      </c>
+      <c r="AQ4">
+        <v>15.15151515151515</v>
       </c>
     </row>
   </sheetData>
